--- a/Sheets/shift_in_omega_a.xlsx
+++ b/Sheets/shift_in_omega_a.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10814"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samuelgrant/Documents/gm2/EDM/Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C190B86-9DAB-5C49-9DA9-EB6456996E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674F31E4-861F-0449-957C-2C1A59C3F159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="16440" xr2:uid="{793A8B24-C83D-BA45-936E-5675965ECF7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Variable</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t>fractional shift</t>
+  </si>
+  <si>
+    <t>omega_eta</t>
+  </si>
+  <si>
+    <t>omega_tot</t>
   </si>
 </sst>
 </file>
@@ -423,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A968B1A7-5D75-D74E-A207-2A05936D068B}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -534,6 +540,30 @@
         <v>1.7703905537798017E-3</v>
       </c>
     </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <f>C12+B9</f>
+        <v>1.4410813905537798</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15">
+        <f>SQRT(C13^2-B9^2)</f>
+        <v>7.1410219712696676E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <f>2*PI()/C15</f>
+        <v>87.987200325928157</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
